--- a/Example_Memory_Map.xlsx
+++ b/Example_Memory_Map.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="36">
   <si>
     <t xml:space="preserve">Member ID</t>
   </si>
@@ -35,10 +35,10 @@
     <t xml:space="preserve">Units</t>
   </si>
   <si>
-    <t xml:space="preserve">Limit Min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limit Max</t>
+    <t xml:space="preserve">Min Limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Limit</t>
   </si>
   <si>
     <t xml:space="preserve">Default</t>
@@ -95,13 +95,40 @@
     <t xml:space="preserve">RO</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTOGEN</t>
+    <t xml:space="preserve">49856</t>
   </si>
   <si>
     <t xml:space="preserve">Memory Map Gen Time</t>
   </si>
   <si>
+    <t xml:space="preserve">float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Memory Map Checksum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int8_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint16_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int32_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-655346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0001</t>
   </si>
 </sst>
 </file>
@@ -117,6 +144,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -189,8 +217,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -388,311 +420,311 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="27.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="27.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="2"/>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="2"/>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="2"/>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="2"/>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="2"/>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="2"/>
+      <c r="H7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="2"/>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="2"/>
+      <c r="D9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -723,311 +755,311 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="27.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="27.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="2"/>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="2"/>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="2"/>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="2"/>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="2"/>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="2"/>
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="2"/>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="2"/>
+      <c r="D9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="2">
